--- a/data/classifier.xlsx
+++ b/data/classifier.xlsx
@@ -2196,7 +2196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1133"/>
+  <dimension ref="A1:F1132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35804,7 +35804,7 @@
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
-          <t>23060001</t>
+          <t>24010000</t>
         </is>
       </c>
       <c r="B1121" t="inlineStr">
@@ -35814,23 +35814,27 @@
       </c>
       <c r="C1121" t="inlineStr">
         <is>
-          <t>Прочие происшествия (от 102)</t>
+          <t>БПЛА</t>
         </is>
       </c>
       <c r="D1121" t="inlineStr">
         <is>
-          <t>{"level1": "Прочие происшествия (от 102)", "level2": "Для простомотра операторов ОКр"}</t>
+          <t>{"level1": "готовят к запуску, летит"}</t>
         </is>
       </c>
       <c r="E1121" t="n">
-        <v>3</v>
-      </c>
-      <c r="F1121" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>S102,FSB,CODD,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB,MO_RHBZ</t>
+        </is>
+      </c>
     </row>
     <row r="1122">
       <c r="A1122" t="inlineStr">
         <is>
-          <t>24010000</t>
+          <t>24020000</t>
         </is>
       </c>
       <c r="B1122" t="inlineStr">
@@ -35840,27 +35844,27 @@
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>БПЛА</t>
+          <t>БПЛА здание</t>
         </is>
       </c>
       <c r="D1122" t="inlineStr">
         <is>
-          <t>{"level1": "готовят к запуску, летит"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "жилой дом/административное здание"}</t>
         </is>
       </c>
       <c r="E1122" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
-          <t>S102,FSB,CODD,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB,MO_RHBZ</t>
+          <t>S102,S104,FSB,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,DEP_GRSTROY,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,DGP,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
         <is>
-          <t>24020000</t>
+          <t>24030000</t>
         </is>
       </c>
       <c r="B1123" t="inlineStr">
@@ -35870,27 +35874,27 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>БПЛА здание</t>
+          <t>БПЛА проезжая часть</t>
         </is>
       </c>
       <c r="D1123" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "жилой дом/административное здание"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "проезжая часть/тоннель/Мост/Эстакада/Подземный переход/Наземный переход"}</t>
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,DEP_GRSTROY,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,DGP,CUKB</t>
+          <t>S102,S104,FSB,AVTODOR,GORMOST,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1124">
       <c r="A1124" t="inlineStr">
         <is>
-          <t>24030000</t>
+          <t>24040000</t>
         </is>
       </c>
       <c r="B1124" t="inlineStr">
@@ -35900,12 +35904,12 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>БПЛА проезжая часть</t>
+          <t>БПЛА учебное заведение</t>
         </is>
       </c>
       <c r="D1124" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "проезжая часть/тоннель/Мост/Эстакада/Подземный переход/Наземный переход"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Учебное"}</t>
         </is>
       </c>
       <c r="E1124" t="n">
@@ -35913,14 +35917,14 @@
       </c>
       <c r="F1124" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,AVTODOR,GORMOST,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,FSB,MOSVODOKANAL,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,DEP_OBR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1125">
       <c r="A1125" t="inlineStr">
         <is>
-          <t>24040000</t>
+          <t>24050000</t>
         </is>
       </c>
       <c r="B1125" t="inlineStr">
@@ -35930,27 +35934,27 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>БПЛА учебное заведение</t>
+          <t>БПЛА лечебное заведение</t>
         </is>
       </c>
       <c r="D1125" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Учебное"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Лечебное"}</t>
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,MOSVODOKANAL,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,DEP_OBR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,CEMP,FSB,MOSVODOKANAL,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1126">
       <c r="A1126" t="inlineStr">
         <is>
-          <t>24050000</t>
+          <t>24060000</t>
         </is>
       </c>
       <c r="B1126" t="inlineStr">
@@ -35960,27 +35964,27 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>БПЛА лечебное заведение</t>
+          <t>БПЛА коммуникации, объект связи</t>
         </is>
       </c>
       <c r="D1126" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Лечебное"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Коммуникации/Объект связи"}</t>
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
-          <t>S102,S104,CEMP,FSB,MOSVODOKANAL,ROSSETI,OEK,CODD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1127">
       <c r="A1127" t="inlineStr">
         <is>
-          <t>24060000</t>
+          <t>24070000</t>
         </is>
       </c>
       <c r="B1127" t="inlineStr">
@@ -35990,12 +35994,12 @@
       </c>
       <c r="C1127" t="inlineStr">
         <is>
-          <t>БПЛА коммуникации, объект связи</t>
+          <t>БПЛА Опасный объект, газопровод</t>
         </is>
       </c>
       <c r="D1127" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Коммуникации/Объект связи"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Опасный объект/Газопровод"}</t>
         </is>
       </c>
       <c r="E1127" t="n">
@@ -36003,14 +36007,14 @@
       </c>
       <c r="F1127" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S101,S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB,MO_RHBZ</t>
         </is>
       </c>
     </row>
     <row r="1128">
       <c r="A1128" t="inlineStr">
         <is>
-          <t>24070000</t>
+          <t>24080000</t>
         </is>
       </c>
       <c r="B1128" t="inlineStr">
@@ -36020,27 +36024,27 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>БПЛА Опасный объект, газопровод</t>
+          <t>БПЛА ЛЭП/Провода/контактная сеть</t>
         </is>
       </c>
       <c r="D1128" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Опасный объект/Газопровод"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "ЛЭП/Провода/ Контактная сеть"}</t>
         </is>
       </c>
       <c r="E1128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
-          <t>S101,S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB,MO_RHBZ</t>
+          <t>S102,S104,FSB,METRO,ROSSETI,OEK,CODD,RZD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1129">
       <c r="A1129" t="inlineStr">
         <is>
-          <t>24080000</t>
+          <t>24090000</t>
         </is>
       </c>
       <c r="B1129" t="inlineStr">
@@ -36050,27 +36054,27 @@
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>БПЛА ЛЭП/Провода/контактная сеть</t>
+          <t>БПЛА Транспорный объект</t>
         </is>
       </c>
       <c r="D1129" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "ЛЭП/Провода/ Контактная сеть"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Транспортный объект"}</t>
         </is>
       </c>
       <c r="E1129" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1129" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,METRO,ROSSETI,OEK,CODD,RZD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,FSB,MOSGORTRANS,MGTS,METRO,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,RZD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,ORG_PEREVOZOK,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1130">
       <c r="A1130" t="inlineStr">
         <is>
-          <t>24090000</t>
+          <t>24100000</t>
         </is>
       </c>
       <c r="B1130" t="inlineStr">
@@ -36080,27 +36084,27 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>БПЛА Транспорный объект</t>
+          <t>БПЛА Военный объект</t>
         </is>
       </c>
       <c r="D1130" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Транспортный объект"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Военный объект"}</t>
         </is>
       </c>
       <c r="E1130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1130" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,MOSGORTRANS,MGTS,METRO,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,RZD,OATI,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,ORG_PEREVOZOK,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
-          <t>24100000</t>
+          <t>24110000</t>
         </is>
       </c>
       <c r="B1131" t="inlineStr">
@@ -36110,27 +36114,27 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>БПЛА Военный объект</t>
+          <t>БПЛА Прочее</t>
         </is>
       </c>
       <c r="D1131" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Военный объект"}</t>
+          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Прочее"}</t>
         </is>
       </c>
       <c r="E1131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F1131" t="inlineStr">
         <is>
-          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
+          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
         </is>
       </c>
     </row>
     <row r="1132">
       <c r="A1132" t="inlineStr">
         <is>
-          <t>24110000</t>
+          <t>24120100</t>
         </is>
       </c>
       <c r="B1132" t="inlineStr">
@@ -36140,48 +36144,18 @@
       </c>
       <c r="C1132" t="inlineStr">
         <is>
-          <t>БПЛА Прочее</t>
+          <t>БПЛА Регион</t>
         </is>
       </c>
       <c r="D1132" t="inlineStr">
         <is>
-          <t>{"level1": "упал/ столкнулся, нет взрыва возгорания", "level2": "Прочее"}</t>
+          <t>{"level1": "летит, готовят к запуску,упал/ столкнулся, нет взрыва возгорания", "level2": "Регион"}</t>
         </is>
       </c>
       <c r="E1132" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F1132" t="inlineStr">
-        <is>
-          <t>S102,S104,FSB,MGTS,MOSVODOKANAL,MOEK,ROSSETI,OEK,CODD,MOSKOLLEKTOR,OATI,MOSVODOSTOK,ROSGVARDIA,DDS_DISTRICT,DDS_TINAO,CITYENERGO,RBIPK,MAYOR,KOMENDATURA,NTU,FSO,GUP_MSR,CUKB</t>
-        </is>
-      </c>
-    </row>
-    <row r="1133">
-      <c r="A1133" t="inlineStr">
-        <is>
-          <t>24120100</t>
-        </is>
-      </c>
-      <c r="B1133" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C1133" t="inlineStr">
-        <is>
-          <t>БПЛА Регион</t>
-        </is>
-      </c>
-      <c r="D1133" t="inlineStr">
-        <is>
-          <t>{"level1": "летит, готовят к запуску,упал/ столкнулся, нет взрыва возгорания", "level2": "Регион"}</t>
-        </is>
-      </c>
-      <c r="E1133" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1133" t="inlineStr">
         <is>
           <t>S102,FSB,CITYENERGO,MAYOR,NTU,FSO,GUP_MSR,CUKB,MO_RHBZ</t>
         </is>

--- a/data/classifier.xlsx
+++ b/data/classifier.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1807,3962 @@
       </c>
       <c r="E59" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DIR_001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ОГДЦ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ОГДЦ</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DIR_002</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>АСУ НС (Автоматизированная система управления)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>АСУ НС</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DIR_003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Мос.Без. (Московская Безопасность)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Мос.Без.</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DIR_004</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>112 Мос. обл. (112 Московской области)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>112 Мос. обл.</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DIR_005</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Северное (ДДС района Чертаново Северное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Северное</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DIR_006</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Поселение Академический (ДДС Академического района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Поселение Академический</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DIR_007</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Поселение Ломоносовский (ДДС Ломоносовского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Поселение Ломоносовский</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DIR_008</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Поселение Бибирево (ДДС района Бибирево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Поселение Бибирево</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DIR_009</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Поселение ЮВАО (ДДС префектуры Юго-Восточного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Поселение ЮВАО</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DIR_010</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Поселение ВАО (ДДС префектуры Восточного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Поселение ВАО</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DIR_011</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Поселение Зябликово (ДДС района Зябликово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Поселение Зябликово</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DIR_012</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Поселение Силино (ДДС района Силино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Поселение Силино</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DIR_013</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Упр. района Вешняки (ДДС района Вешняки города Москвы)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Упр. района Вешняки</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DIR_014</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Поселение Крюково (ДДС района Крюково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Поселение Крюково</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DIR_015</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Поселение Матушкино (ДДС района Матушкино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Поселение Матушкино</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DIR_016</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Поселение Новогиреево (ДДС района Новогиреево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Поселение Новогиреево</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DIR_017</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Поселение Савелки (ДДС района Савелки города Москвы)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Поселение Савелки</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DIR_018</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Поселение Старое Крюково (ДДС района Старое Крюково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Поселение Старое Крюково</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DIR_019</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Южное (ДДС района Чертаново Южное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Южное</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DIR_020</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Поселение Теплый Стан (ДДС района Теплый Стан города Москвы)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Поселение Теплый Стан</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DIR_021</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Поселение Рязанский (ДДС Рязанского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Поселение Рязанский</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DIR_022</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Поселение ЗелАО (ДДС префектуры Зеленоградского административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Поселение ЗелАО</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DIR_023</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Поселение Печатники (ДДС района Печатники города Москвы)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Поселение Печатники</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DIR_024</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Поселение САО (ДДС префектуры Северного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Поселение САО</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DIR_025</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Поселение Новокосино (ДДС района Новокосино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Поселение Новокосино</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DIR_026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Поселение Царицыно (ДДС района Царицыно города Москвы)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Поселение Царицыно</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DIR_027</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Поселение Марьино (ДДС района Марьино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Поселение Марьино</t>
+        </is>
+      </c>
+      <c r="D86" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DIR_028</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Поселение Кузьминки (ДДС района Кузьминки города Москвы)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Поселение Кузьминки</t>
+        </is>
+      </c>
+      <c r="D87" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DIR_029</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Поселение Митино (ДДС района Митино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Поселение Митино</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DIR_030</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Поселение Савеловский (ДДС Савеловского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Поселение Савеловский</t>
+        </is>
+      </c>
+      <c r="D89" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DIR_031</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Поселение Щукино (ДДС района Щукино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Поселение Щукино</t>
+        </is>
+      </c>
+      <c r="D90" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DIR_032</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Поселение Покровское-Стрешнево (ДДС района Покровское-Стрешнево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Поселение Покровское-Стрешнево</t>
+        </is>
+      </c>
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DIR_033</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Поселение Первомайское (ДДС поселения Первомайское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Поселение Первомайское</t>
+        </is>
+      </c>
+      <c r="D92" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DIR_034</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>112 Кал. обл. (112 Калужская область)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>112 Кал. обл.</t>
+        </is>
+      </c>
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DIR_035</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Поселение Северное Тушино (ДДС района Северное Тушино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Поселение Северное Тушино</t>
+        </is>
+      </c>
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DIR_036</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Поселение Нагатинский Затон (ДДС района Нагатинский Затон города Москвы)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Поселение Нагатинский Затон</t>
+        </is>
+      </c>
+      <c r="D95" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DIR_037</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Поселение Дорогомилово (ДДС района Дорогомилово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Поселение Дорогомилово</t>
+        </is>
+      </c>
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DIR_038</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Поселение Коптево (ДДС района Коптево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Поселение Коптево</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DIR_039</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Поселение Крылатское (ДДС района Крылатское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Поселение Крылатское</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DIR_040</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Поселение Тверской (ДДС Тверского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Поселение Тверской</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DIR_041</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Поселение Внуково (ДДС района Внуково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Поселение Внуково</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DIR_042</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Поселение Ярославский (ДДС Ярославского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Поселение Ярославский</t>
+        </is>
+      </c>
+      <c r="D101" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DIR_043</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Поселение ЮАО (ДДС префектуры Южного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Поселение ЮАО</t>
+        </is>
+      </c>
+      <c r="D102" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DIR_044</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Поселение Михайлово-Ярцевское (ДДС поселения Михайлово-Ярцевское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Поселение Михайлово-Ярцевское</t>
+        </is>
+      </c>
+      <c r="D103" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DIR_045</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Поселение Некрасовка (ДДС района Некрасовка города Москвы)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Поселение Некрасовка</t>
+        </is>
+      </c>
+      <c r="D104" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DIR_046</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Поселение Выхино-Жулебино (ДДС района Выхино-Жулебино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Поселение Выхино-Жулебино</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DIR_047</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Поселение Москворечье-Сабурово (ДДС района Москворечье-Сабурово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Поселение Москворечье-Сабурово</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DIR_048</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Поселение ЮЗАО (ДДС префектура Юго-Западного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Поселение ЮЗАО</t>
+        </is>
+      </c>
+      <c r="D107" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DIR_049</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Поселение Донской (ДДС Донского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Поселение Донской</t>
+        </is>
+      </c>
+      <c r="D108" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DIR_050</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Поселение Куркино (ДДС района Куркино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Поселение Куркино</t>
+        </is>
+      </c>
+      <c r="D109" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DIR_051</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Поселение Южное Бутово (ДДС района Южное Бутово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Поселение Южное Бутово</t>
+        </is>
+      </c>
+      <c r="D110" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>DIR_052</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Поселение Лианозово (ДДС района Лианозово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Поселение Лианозово</t>
+        </is>
+      </c>
+      <c r="D111" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>DIR_053</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Поселение Лефортово (ДДС района Лефортово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Поселение Лефортово</t>
+        </is>
+      </c>
+      <c r="D112" t="b">
+        <v>1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>DIR_054</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Поселение Замоскворечье (ДДС района Замоскворечье города Москвы)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Поселение Замоскворечье</t>
+        </is>
+      </c>
+      <c r="D113" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>DIR_055</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Поселение СВАО (ДДС префектуры Северо-Восточного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Поселение СВАО</t>
+        </is>
+      </c>
+      <c r="D114" t="b">
+        <v>1</v>
+      </c>
+      <c r="E114" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>DIR_056</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Поселение Сокольники (ДДС района Сокольники города Москвы)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Поселение Сокольники</t>
+        </is>
+      </c>
+      <c r="D115" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DIR_057</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Поселение Измайлово (ДДС района Измайлово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Поселение Измайлово</t>
+        </is>
+      </c>
+      <c r="D116" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>DIR_058</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Поселение Богородское (ДДС района Богородское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Поселение Богородское</t>
+        </is>
+      </c>
+      <c r="D117" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DIR_059</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Поселение Преображенский (ДДС района Преображенское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Поселение Преображенский</t>
+        </is>
+      </c>
+      <c r="D118" t="b">
+        <v>1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DIR_060</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Поселение Восточное Измайлово (ДДС района Восточное Измайлово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Поселение Восточное Измайлово</t>
+        </is>
+      </c>
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DIR_061</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Поселение Ростокино (ДДС района Ростокино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Поселение Ростокино</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>DIR_062</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Поселение Соколиная гора (ДДС района Соколиная гора города Москвы)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Поселение Соколиная гора</t>
+        </is>
+      </c>
+      <c r="D121" t="b">
+        <v>1</v>
+      </c>
+      <c r="E121" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>DIR_063</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Поселение Хорошево-Мневники (ДДС района Хорошево-Мневники города Москвы)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Поселение Хорошево-Мневники</t>
+        </is>
+      </c>
+      <c r="D122" t="b">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>DIR_064</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Поселение Гольяново (ДДС района Гольяново города Москвы)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Поселение Гольяново</t>
+        </is>
+      </c>
+      <c r="D123" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>DIR_065</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Поселение Северное Измайлово (ДДС района Северное Измайлово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Поселение Северное Измайлово</t>
+        </is>
+      </c>
+      <c r="D124" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>DIR_066</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Поселение Марфино (ДДС района Марфино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Поселение Марфино</t>
+        </is>
+      </c>
+      <c r="D125" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DIR_067</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Поселение Метрогородок (ДДС района Метрогородок города Москвы)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Поселение Метрогородок</t>
+        </is>
+      </c>
+      <c r="D126" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DIR_068</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Поселение Фили-Давыдково (ДДС района Фили-Давыдково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Поселение Фили-Давыдково</t>
+        </is>
+      </c>
+      <c r="D127" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>DIR_069</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Поселение Южное Медведково (ДДС района Южное Медведково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Поселение Южное Медведково</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>DIR_070</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Поселение Рязановское (ДДС поселения Рязановское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Поселение Рязановское</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>DIR_071</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Поселение Тимирязевский (ДДС Тимирязевского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Поселение Тимирязевский</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>DIR_072</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Поселение Бирюлево Западное (ДДС района Бирюлево Западное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Поселение Бирюлево Западное</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>DIR_073</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Поселение Ивановский (ДДС Ивановского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Поселение Ивановский</t>
+        </is>
+      </c>
+      <c r="D132" t="b">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>DIR_074</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Поселение Ново-Переделкино (ДДС района Ново-Переделкино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Поселение Ново-Переделкино</t>
+        </is>
+      </c>
+      <c r="D133" t="b">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DIR_075</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Поселение Восточное Дегунино (ДДС района Восточное Дегунино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Поселение Восточное Дегунино</t>
+        </is>
+      </c>
+      <c r="D134" t="b">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>DIR_076</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Поселение Ховрино (ДДС района Ховрино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Поселение Ховрино</t>
+        </is>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>DIR_077</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Поселение Головинский (ДДС Головинского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Поселение Головинский</t>
+        </is>
+      </c>
+      <c r="D136" t="b">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>DIR_078</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Поселение Бескудниково (ДДС Бескудниковского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Поселение Бескудниково</t>
+        </is>
+      </c>
+      <c r="D137" t="b">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>DIR_079</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Поселение Левобережный (ДДС района Левобережный города Москвы)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Поселение Левобережный</t>
+        </is>
+      </c>
+      <c r="D138" t="b">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>DIR_080</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Поселение Дмитровский (ДДС Дмитровского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Поселение Дмитровский</t>
+        </is>
+      </c>
+      <c r="D139" t="b">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>DIR_081</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Поселение Сокол (ДДС района Сокол города Москвы)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Поселение Сокол</t>
+        </is>
+      </c>
+      <c r="D140" t="b">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>DIR_082</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Поселение Молжаниновский (ДДС Молжаниновского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Поселение Молжаниновский</t>
+        </is>
+      </c>
+      <c r="D141" t="b">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>DIR_083</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Поселение Хамовники (ДДС района Хамовники города Москвы)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Поселение Хамовники</t>
+        </is>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DIR_084</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Поселение Басманный (ДДС Басманного района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Поселение Басманный</t>
+        </is>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DIR_085</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Поселение Якиманка (ДДС района Якиманка города Москвы)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Поселение Якиманка</t>
+        </is>
+      </c>
+      <c r="D144" t="b">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>DIR_086</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Поселение Мещанский (ДДС Мещанского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Поселение Мещанский</t>
+        </is>
+      </c>
+      <c r="D145" t="b">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>DIR_087</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Поселение Пресненский (ДДС Пресненского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Поселение Пресненский</t>
+        </is>
+      </c>
+      <c r="D146" t="b">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>DIR_088</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Поселение Мосрентген (ДДС поселения «Мосрентген» в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Поселение Мосрентген</t>
+        </is>
+      </c>
+      <c r="D147" t="b">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DIR_089</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Поселение Ясенево (ДДС района Ясенево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Поселение Ясенево</t>
+        </is>
+      </c>
+      <c r="D148" t="b">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DIR_090</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Поселение Щербинка (ДДС городского округа Щербинка города Москвы)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Поселение Щербинка</t>
+        </is>
+      </c>
+      <c r="D149" t="b">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DIR_091</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Поселение Капотня (ДДС района Капотня города Москвы)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Поселение Капотня</t>
+        </is>
+      </c>
+      <c r="D150" t="b">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DIR_092</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Поселение Троицк (ДДС городского округа Троицк города Москвы)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Поселение Троицк</t>
+        </is>
+      </c>
+      <c r="D151" t="b">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>DIR_093</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Поселение Нагатино-Садовники (ДДС района Нагатино Садовники)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Поселение Нагатино-Садовники</t>
+        </is>
+      </c>
+      <c r="D152" t="b">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DIR_094</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Поселение Клёновское (ДДС поселения Клёновское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Поселение Клёновское</t>
+        </is>
+      </c>
+      <c r="D153" t="b">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DIR_095</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Поселение Нагорный (ДДС района Нагорный города Москвы)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Поселение Нагорный</t>
+        </is>
+      </c>
+      <c r="D154" t="b">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>DIR_096</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Поселение Бабушкинский (ДДС Бабушкинского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Поселение Бабушкинский</t>
+        </is>
+      </c>
+      <c r="D155" t="b">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DIR_097</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Поселение Бутырский (ДДС Бутырского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Поселение Бутырский</t>
+        </is>
+      </c>
+      <c r="D156" t="b">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>DIR_098</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Поселение Лосиноостровский (ДДС Лосиноостровского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Поселение Лосиноостровский</t>
+        </is>
+      </c>
+      <c r="D157" t="b">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>DIR_099</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Поселение Останкинский (ДДС Останкинского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Поселение Останкинский</t>
+        </is>
+      </c>
+      <c r="D158" t="b">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>DIR_100</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Поселение Отрадное (ДДС района Отрадное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Поселение Отрадное</t>
+        </is>
+      </c>
+      <c r="D159" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>DIR_101</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Поселение Свиблово (ДДС района Свиблово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Поселение Свиблово</t>
+        </is>
+      </c>
+      <c r="D160" t="b">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>DIR_102</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Поселение Северное Медведково (ДДС района Северное Медведково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Поселение Северное Медведково</t>
+        </is>
+      </c>
+      <c r="D161" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>DIR_103</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Поселение Северный (ДДС района Северный города Москвы)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Поселение Северный</t>
+        </is>
+      </c>
+      <c r="D162" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>DIR_104</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Поселение Орехово-Борисово Северное (ДДС района Орехово-Борисово Северное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Поселение Орехово-Борисово Северное</t>
+        </is>
+      </c>
+      <c r="D163" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>DIR_105</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Поселение Перово (ДДС района Перово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Поселение Перово</t>
+        </is>
+      </c>
+      <c r="D164" t="b">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>DIR_106</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Поселение Алтуфьевский (ДДС Алтуфьевского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Поселение Алтуфьевский</t>
+        </is>
+      </c>
+      <c r="D165" t="b">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>DIR_107</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Поселение Можайский (ДДС Можайского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Поселение Можайский</t>
+        </is>
+      </c>
+      <c r="D166" t="b">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DIR_108</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Поселение Раменки (ДДС района Раменки города Москвы)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Поселение Раменки</t>
+        </is>
+      </c>
+      <c r="D167" t="b">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>DIR_109</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Поселение Алексеевский (ДДС Алексеевского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Поселение Алексеевский</t>
+        </is>
+      </c>
+      <c r="D168" t="b">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>DIR_110</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Поселение Кунцево (ДДС района Кунцево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Поселение Кунцево</t>
+        </is>
+      </c>
+      <c r="D169" t="b">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>DIR_111</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Поселение Тропарево-Никулино (ДДС района Тропарево-Никулино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Поселение Тропарево-Никулино</t>
+        </is>
+      </c>
+      <c r="D170" t="b">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>DIR_112</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Поселение Восточный (ДДС района Восточный города Москвы)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Поселение Восточный</t>
+        </is>
+      </c>
+      <c r="D171" t="b">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>DIR_113</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Поселение Аэропорт (ДДС района Аэропорт города Москвы)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Поселение Аэропорт</t>
+        </is>
+      </c>
+      <c r="D172" t="b">
+        <v>1</v>
+      </c>
+      <c r="E172" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>DIR_114</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Поселение Западное Дегунино (ДДС района Западное Дегунино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Поселение Западное Дегунино</t>
+        </is>
+      </c>
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>DIR_115</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Поселение Войковский (ДДС Войковского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Поселение Войковский</t>
+        </is>
+      </c>
+      <c r="D174" t="b">
+        <v>1</v>
+      </c>
+      <c r="E174" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>DIR_116</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Поселение Хорошевский (ДДС Хорошевского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Поселение Хорошевский</t>
+        </is>
+      </c>
+      <c r="D175" t="b">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>DIR_117</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Поселение Беговой (ДДС района Беговой города Москвы)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Поселение Беговой</t>
+        </is>
+      </c>
+      <c r="D176" t="b">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DIR_118</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Поселение Текстильщики (ДДС района Текстильщики города Москвы)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Поселение Текстильщики</t>
+        </is>
+      </c>
+      <c r="D177" t="b">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DIR_119</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Поселение Московское (ДДС поселения Московский в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Поселение Московское</t>
+        </is>
+      </c>
+      <c r="D178" t="b">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>DIR_120</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Поселение Братеево (ДДС района Братеево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Поселение Братеево</t>
+        </is>
+      </c>
+      <c r="D179" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>DIR_121</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Поселение Филимонковское (ДДС поселения Филимонковское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Поселение Филимонковское</t>
+        </is>
+      </c>
+      <c r="D180" t="b">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>DIR_122</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Поселение Люблино (ДДС района Люблино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Поселение Люблино</t>
+        </is>
+      </c>
+      <c r="D181" t="b">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DIR_123</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Поселение Марушкинское (ДДС поселения Марушкинское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Поселение Марушкинское</t>
+        </is>
+      </c>
+      <c r="D182" t="b">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DIR_124</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Поселение Орехово-Борисово Южное (ДДС района Орехово-Борисово Южное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Поселение Орехово-Борисово Южное</t>
+        </is>
+      </c>
+      <c r="D183" t="b">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DIR_125</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Поселение Даниловский (ДДС Даниловского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Поселение Даниловский</t>
+        </is>
+      </c>
+      <c r="D184" t="b">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DIR_126</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Поселение Роговское (ДДС поселения Роговское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Поселение Роговское</t>
+        </is>
+      </c>
+      <c r="D185" t="b">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>DIR_127</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Поселение ЗАО (ДДС префектуры Западного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Поселение ЗАО</t>
+        </is>
+      </c>
+      <c r="D186" t="b">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>DIR_128</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Поселение Нижегородский (ДДС Нижегородского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Поселение Нижегородский</t>
+        </is>
+      </c>
+      <c r="D187" t="b">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>DIR_129</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Поселение Щаповское (ДДС поселения Щаповское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Поселение Щаповское</t>
+        </is>
+      </c>
+      <c r="D188" t="b">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>DIR_130</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Поселение Южнопортовый (ДДС Южнопортового района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Поселение Южнопортовый</t>
+        </is>
+      </c>
+      <c r="D189" t="b">
+        <v>1</v>
+      </c>
+      <c r="E189" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>DIR_131</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Поселение ЦАО (ДДС префектуры Центрального административного округа)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Поселение ЦАО</t>
+        </is>
+      </c>
+      <c r="D190" t="b">
+        <v>1</v>
+      </c>
+      <c r="E190" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>DIR_132</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Поселение Черемушки (ДДС района Черемушки города Москвы)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Поселение Черемушки</t>
+        </is>
+      </c>
+      <c r="D191" t="b">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>DIR_133</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Поселение Марьина роща (ДДС района Марьина роща города Москвы)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Поселение Марьина роща</t>
+        </is>
+      </c>
+      <c r="D192" t="b">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>DIR_134</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Поселение Красносельский (ДДС Красносельского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Поселение Красносельский</t>
+        </is>
+      </c>
+      <c r="D193" t="b">
+        <v>1</v>
+      </c>
+      <c r="E193" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DIR_135</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Поселение Строгино (ДДС района Строгино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Поселение Строгино</t>
+        </is>
+      </c>
+      <c r="D194" t="b">
+        <v>1</v>
+      </c>
+      <c r="E194" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>DIR_136</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Поселение СЗАО (ДДС префектуры Северо-Западного административного округа города Москвы)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Поселение СЗАО</t>
+        </is>
+      </c>
+      <c r="D195" t="b">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>DIR_137</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Поселение Бирюлево Восточное (ДДС района Бирюлево Восточное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Поселение Бирюлево Восточное</t>
+        </is>
+      </c>
+      <c r="D196" t="b">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>DIR_138</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Центральное (ДДС района Чертаново Центральное города Москвы)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Поселение Чертаново Центральное</t>
+        </is>
+      </c>
+      <c r="D197" t="b">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>DIR_139</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Поселение Гагаринский (ДДС Гагаринского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Поселение Гагаринский</t>
+        </is>
+      </c>
+      <c r="D198" t="b">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>DIR_140</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Поселение Обручевский (ДДС Обручевского района города Москвы)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Поселение Обручевский</t>
+        </is>
+      </c>
+      <c r="D199" t="b">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>DIR_141</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Поселение Зюзино (ДДС района Зюзино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Поселение Зюзино</t>
+        </is>
+      </c>
+      <c r="D200" t="b">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DIR_142</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Поселение Коньково (ДДС района Коньково города Москвы)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Поселение Коньково</t>
+        </is>
+      </c>
+      <c r="D201" t="b">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DIR_143</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Поселение Котловка (ДДС района Котловка города Москвы)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Поселение Котловка</t>
+        </is>
+      </c>
+      <c r="D202" t="b">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DIR_144</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Поселение Северное Бутово (ДДС района Северное Бутово города Москвы)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Поселение Северное Бутово</t>
+        </is>
+      </c>
+      <c r="D203" t="b">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DIR_145</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Поселение Косино-Ухтомский (ДДС района Косино-Ухтомский города Москвы)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Поселение Косино-Ухтомский</t>
+        </is>
+      </c>
+      <c r="D204" t="b">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DIR_146</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Поселение Солнцево (ДДС района Солнцево города Москвы)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Поселение Солнцево</t>
+        </is>
+      </c>
+      <c r="D205" t="b">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DIR_147</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Поселение Таганский (ДДС района Таганский города Москвы)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Поселение Таганский</t>
+        </is>
+      </c>
+      <c r="D206" t="b">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>DIR_148</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Поселение Очаково-Матвеевское (ДДС района Очаково-Матвеевское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Поселение Очаково-Матвеевское</t>
+        </is>
+      </c>
+      <c r="D207" t="b">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>DIR_149</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Поселение Южное Тушино (ДДС района Южное Тушино города Москвы)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Поселение Южное Тушино</t>
+        </is>
+      </c>
+      <c r="D208" t="b">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>DIR_150</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Поселение Филевский парк (ДДС района Филевский парк города Москвы)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Поселение Филевский парк</t>
+        </is>
+      </c>
+      <c r="D209" t="b">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>DIR_151</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Поселение Проспект Вернадского (ДДС района Проспект Вернадского города Москвы)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Поселение Проспект Вернадского</t>
+        </is>
+      </c>
+      <c r="D210" t="b">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>DIR_152</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Поселение Десеновское (ДДС поселения Десеновское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Поселение Десеновское</t>
+        </is>
+      </c>
+      <c r="D211" t="b">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>DIR_153</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Поселение Арбат (ДДС района Арбат города Москвы)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Поселение Арбат</t>
+        </is>
+      </c>
+      <c r="D212" t="b">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>DIR_154</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Дежурно-диспетчерская служба (Дежурно-диспетчерская служба)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Дежурно-диспетчерская служба</t>
+        </is>
+      </c>
+      <c r="D213" t="b">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>DIR_155</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Поселение Сосенское (ДДС поселения Сосенское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Поселение Сосенское</t>
+        </is>
+      </c>
+      <c r="D214" t="b">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>DIR_156</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Поселение Кокошкино (ДДС поселения Кокошкино в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Поселение Кокошкино</t>
+        </is>
+      </c>
+      <c r="D215" t="b">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>DIR_157</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Поселение Воскресенское (ДДС поселения Воскресенское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Поселение Воскресенское</t>
+        </is>
+      </c>
+      <c r="D216" t="b">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>DIR_158</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Поселение Краснопахорское (ДДС поселения Краснопахорское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Поселение Краснопахорское</t>
+        </is>
+      </c>
+      <c r="D217" t="b">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>DIR_159</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Поселение Вороновское (ДДС поселения Вороновское в городе Москве)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Поселение Вороновское</t>
+        </is>
+      </c>
+      <c r="D218" t="b">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>DIR_160</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Поселение Внуковское (ДДС поселения Внуковское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Поселение Внуковское</t>
+        </is>
+      </c>
+      <c r="D219" t="b">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>DIR_161</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Поселение Новофедоровское (ДДС поселения Новофедоровское города Москвы)</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Поселение Новофедоровское</t>
+        </is>
+      </c>
+      <c r="D220" t="b">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>DIR_162</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Поселение Киевский (ДДС поселения Киевский города Москвы)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Поселение Киевский</t>
+        </is>
+      </c>
+      <c r="D221" t="b">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>DIR_163</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ГБУ АД ВАО (ГБУ Автодороги ВАО)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ГБУ АД ВАО</t>
+        </is>
+      </c>
+      <c r="D222" t="b">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>DIR_164</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ГБУ АД СВАО (ГБУ Автодороги СВАО)</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ГБУ АД СВАО</t>
+        </is>
+      </c>
+      <c r="D223" t="b">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>DIR_165</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮВАО (ГБУ Автодороги ЮВАО)</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮВАО</t>
+        </is>
+      </c>
+      <c r="D224" t="b">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>DIR_166</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЗелАО (ГБУ Автодороги ЗелАО)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЗелАО</t>
+        </is>
+      </c>
+      <c r="D225" t="b">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>DIR_167</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮЗАО (ГБУ Автодороги ЮЗАО)</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮЗАО</t>
+        </is>
+      </c>
+      <c r="D226" t="b">
+        <v>1</v>
+      </c>
+      <c r="E226" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DIR_168</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮАО (ГБУ Автодороги ЮАО)</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЮАО</t>
+        </is>
+      </c>
+      <c r="D227" t="b">
+        <v>1</v>
+      </c>
+      <c r="E227" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>DIR_169</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ГБУ АД САО (ГБУ Автодороги САО)</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ГБУ АД САО</t>
+        </is>
+      </c>
+      <c r="D228" t="b">
+        <v>1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>DIR_170</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ГБУ АД СЗАО (ГБУ Автодороги СЗАО)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ГБУ АД СЗАО</t>
+        </is>
+      </c>
+      <c r="D229" t="b">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>DIR_171</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЦАО (ГБУ Автодороги ЦАО)</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЦАО</t>
+        </is>
+      </c>
+      <c r="D230" t="b">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DIR_172</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЗАО (ГБУ Автодороги ЗАО)</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ГБУ АД ЗАО</t>
+        </is>
+      </c>
+      <c r="D231" t="b">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
